--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>Level</t>
@@ -162,10 +162,16 @@
     <t>Door to Groin &lt;= 120 Minutes</t>
   </si>
   <si>
-    <t>D2D</t>
+    <t>Door2Door</t>
   </si>
   <si>
     <t>Door to Door</t>
+  </si>
+  <si>
+    <t>Door2Discharge</t>
+  </si>
+  <si>
+    <t>Door to Discharge</t>
   </si>
   <si>
     <t>D2N</t>
@@ -601,7 +607,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -930,6 +936,18 @@
       </c>
       <c r="D27" s="2"/>
     </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/timing-metric-codes-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/timing-metric-codes-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Local RESQ stroke registry CodeSystem generated from enum_models.py for system http://tecnomod-um.org/CodeSystem/timing-metric-codes-cs.</t>
+    <t>Local RESQ stroke registry CodeSystem generated from enum_models.py for system http://qualityregistry.org/CodeSystem/timing-metric-codes-cs.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-timing-metric-codes-cs.xlsx
+++ b/CodeSystem-timing-metric-codes-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
